--- a/001/xy_001_data.xlsx
+++ b/001/xy_001_data.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>

--- a/001/xy_001_data.xlsx
+++ b/001/xy_001_data.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 01:35</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 01:35</t>
         </is>
       </c>
     </row>

--- a/001/xy_001_data.xlsx
+++ b/001/xy_001_data.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:35</t>
+          <t>25/09/2026 01:44</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:35</t>
+          <t>25/09/2026 01:44</t>
         </is>
       </c>
     </row>

--- a/001/xy_001_data.xlsx
+++ b/001/xy_001_data.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The One Regression That Actually Works</t>
+          <t>The Fed and Your Mortgage: Same Decades, Different Months</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Fed sets the direction. Mortgages follow at about two thirds.</t>
+          <t>Linked over decades, loosely linked month to month.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:44</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:44</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>

--- a/001/xy_001_data.xlsx
+++ b/001/xy_001_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Fed and Your Mortgage: Same Decades, Different Months</t>
+          <t>Fed Funds Rate vs 30-Year Mortgage Rate</t>
         </is>
       </c>
     </row>
@@ -488,293 +488,281 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>When the Fed moves, your mortgage follows. Eventually. Mostly.</t>
+          <t>Mortgage rates track the Fed.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Linked over decades, loosely linked month to month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>publication</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://xandyregression.substack.com</t>
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X label</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fed funds rate (%, FRED)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X label</t>
+          <t>X detail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fed funds rate (%, FRED)</t>
+          <t>Effective federal funds rate, %, monthly average, FRED FEDFUNDS, 01/1990 - present</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X detail</t>
+          <t>X source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Effective federal funds rate, %, monthly average, FRED FEDFUNDS, 01/1990 - present</t>
+          <t>FRED FEDFUNDS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X source</t>
+          <t>X source URL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FRED FEDFUNDS</t>
+          <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X source URL</t>
+          <t>X licence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://fred.stlouisfed.org/series/FEDFUNDS</t>
+          <t>open data, redistributed with attribution</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X licence</t>
+          <t>X pulled</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>26/09/2026 19:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>X steps</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>X raw sheet</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>full series as pulled, before any transform</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Y label</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30y mortgage rate (%, Freddie Mac)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Y detail</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30-year fixed mortgage rate, %, weekly averaged to monthly, FRED MORTGAGE30US, 01/1990 - present</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Y source</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>FRED MORTGAGE30US</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Y source URL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://fred.stlouisfed.org/series/MORTGAGE30US</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Y licence</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>open data, redistributed with attribution</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
-          <t>X pulled</t>
+          <t>Y pulled</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
-          <t>25/09/2026 02:03</t>
+          <t>26/09/2026 19:05</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
-          <t>X steps</t>
+          <t>Y steps</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
-          <t>X raw sheet</t>
+          <t>Y raw sheet</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>full series as pulled, before any transform</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
-          <t>Y label</t>
+          <t>join</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
-          <t>30y mortgage rate (%, Freddie Mac)</t>
+          <t>resampled to M by mean</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
-          <t>Y detail</t>
+          <t>lag</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
-          <t>30-year fixed mortgage rate, %, weekly averaged to monthly, FRED MORTGAGE30US, 01/1990 - present</t>
+          <t>X leads Y by 0 periods</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
-          <t>Y source</t>
+          <t>transform</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>FRED MORTGAGE30US</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Y source URL</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://fred.stlouisfed.org/series/MORTGAGE30US</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Y licence</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>open data, redistributed with attribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Y pulled</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>25/09/2026 02:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Y steps</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Y raw sheet</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>full series as pulled, before any transform</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>join</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>resampled to M by mean</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>lag</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>X leads Y by 0 periods</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>p-value</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Newey-West (HAC) for time series</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p-value</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Newey-West (HAC) for time series</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>correlation is not causation</t>
         </is>
